--- a/Master/DATABASE_IA.xlsx
+++ b/Master/DATABASE_IA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEX\DEX-FPnA\Master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{598B54AC-1BA4-414E-936C-6695F0A74BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4658E21C-4B82-47E2-9800-6B957DC307F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{69F88D26-E53E-44EB-8F6B-6F72C75FF8C3}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$343</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$335</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="347">
   <si>
     <t>10.FOOD [BUMBU] - COM V.2</t>
   </si>
@@ -1065,6 +1065,21 @@
   </si>
   <si>
     <t>Packaging Usage</t>
+  </si>
+  <si>
+    <t>PISAU GILING DAGING TC 12</t>
+  </si>
+  <si>
+    <t>PISAU GILING DAGING MHW 80</t>
+  </si>
+  <si>
+    <t>PISAU GILING DAGING MHW 120</t>
+  </si>
+  <si>
+    <t>SENDOK TAKAR STAINLESS 5/15 GRAM</t>
+  </si>
+  <si>
+    <t>SENDOK TAKAR STAINLESS SET</t>
   </si>
 </sst>
 </file>
@@ -1106,7 +1121,26 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1417,7 +1451,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08B8BE52-5B4F-47C1-84A8-24A4E0133727}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B343"/>
+  <dimension ref="A1:B333"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.81640625" bestFit="1" customWidth="1"/>
@@ -1645,7 +1679,7 @@
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
@@ -1653,7 +1687,7 @@
         <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
@@ -1661,7 +1695,7 @@
         <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
@@ -1669,7 +1703,7 @@
         <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
@@ -1677,7 +1711,7 @@
         <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
@@ -1685,7 +1719,7 @@
         <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
@@ -1693,7 +1727,7 @@
         <v>13</v>
       </c>
       <c r="B34" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
@@ -1701,7 +1735,7 @@
         <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
@@ -1709,15 +1743,15 @@
         <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
@@ -1725,7 +1759,7 @@
         <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
@@ -1733,71 +1767,71 @@
         <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B43" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B44" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B47" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
@@ -1805,7 +1839,7 @@
         <v>38</v>
       </c>
       <c r="B48" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
@@ -1813,7 +1847,7 @@
         <v>38</v>
       </c>
       <c r="B49" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
@@ -1821,7 +1855,7 @@
         <v>38</v>
       </c>
       <c r="B50" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
@@ -1829,7 +1863,7 @@
         <v>38</v>
       </c>
       <c r="B51" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
@@ -1837,7 +1871,7 @@
         <v>38</v>
       </c>
       <c r="B52" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
@@ -1845,7 +1879,7 @@
         <v>38</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
@@ -1853,7 +1887,7 @@
         <v>38</v>
       </c>
       <c r="B54" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
@@ -1861,7 +1895,7 @@
         <v>38</v>
       </c>
       <c r="B55" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
@@ -1869,7 +1903,7 @@
         <v>38</v>
       </c>
       <c r="B56" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
@@ -1877,7 +1911,7 @@
         <v>38</v>
       </c>
       <c r="B57" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
@@ -1885,15 +1919,15 @@
         <v>38</v>
       </c>
       <c r="B58" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B59" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
@@ -1901,7 +1935,7 @@
         <v>38</v>
       </c>
       <c r="B60" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
@@ -1909,7 +1943,7 @@
         <v>38</v>
       </c>
       <c r="B61" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
@@ -1917,15 +1951,15 @@
         <v>38</v>
       </c>
       <c r="B62" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
@@ -1933,23 +1967,23 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>56</v>
+        <v>171</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
@@ -1957,23 +1991,23 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>57</v>
+        <v>192</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B68" t="s">
-        <v>58</v>
+        <v>195</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B69" t="s">
-        <v>59</v>
+        <v>207</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
@@ -1981,95 +2015,95 @@
         <v>38</v>
       </c>
       <c r="B70" t="s">
-        <v>60</v>
+        <v>218</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>38</v>
+        <v>232</v>
       </c>
       <c r="B71" t="s">
-        <v>61</v>
+        <v>231</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>63</v>
+        <v>232</v>
       </c>
       <c r="B72" t="s">
-        <v>62</v>
+        <v>233</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>38</v>
+        <v>232</v>
       </c>
       <c r="B73" t="s">
-        <v>83</v>
+        <v>234</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>63</v>
+        <v>232</v>
       </c>
       <c r="B74" t="s">
-        <v>135</v>
+        <v>235</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>63</v>
+        <v>232</v>
       </c>
       <c r="B75" t="s">
-        <v>171</v>
+        <v>236</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>13</v>
+        <v>232</v>
       </c>
       <c r="B76" t="s">
-        <v>191</v>
+        <v>237</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>38</v>
+        <v>232</v>
       </c>
       <c r="B77" t="s">
-        <v>192</v>
+        <v>238</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>13</v>
+        <v>232</v>
       </c>
       <c r="B78" t="s">
-        <v>194</v>
+        <v>239</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>13</v>
+        <v>232</v>
       </c>
       <c r="B79" t="s">
-        <v>195</v>
+        <v>240</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>13</v>
+        <v>232</v>
       </c>
       <c r="B80" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>38</v>
+        <v>232</v>
       </c>
       <c r="B81" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
@@ -2077,15 +2111,15 @@
         <v>232</v>
       </c>
       <c r="B82" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B83" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
@@ -2093,39 +2127,39 @@
         <v>232</v>
       </c>
       <c r="B84" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>232</v>
+        <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>232</v>
+        <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>232</v>
+        <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>232</v>
+        <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
@@ -2133,255 +2167,255 @@
         <v>232</v>
       </c>
       <c r="B89" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>232</v>
+        <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>232</v>
+        <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>232</v>
+        <v>34</v>
       </c>
       <c r="B92" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>232</v>
+        <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B94" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>232</v>
+        <v>38</v>
       </c>
       <c r="B95" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="B96" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B97" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B98" t="s">
-        <v>252</v>
+        <v>284</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B99" t="s">
-        <v>253</v>
+        <v>285</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>232</v>
+        <v>38</v>
       </c>
       <c r="B100" t="s">
-        <v>254</v>
+        <v>294</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B101" t="s">
-        <v>258</v>
+        <v>297</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B102" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B103" t="s">
-        <v>255</v>
+        <v>309</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B104" t="s">
-        <v>262</v>
+        <v>310</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B105" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>13</v>
+        <v>340</v>
       </c>
       <c r="B106" t="s">
-        <v>264</v>
+        <v>64</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>257</v>
+        <v>65</v>
       </c>
       <c r="B107" t="s">
-        <v>265</v>
+        <v>66</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="B108" t="s">
-        <v>266</v>
+        <v>67</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B109" t="s">
-        <v>267</v>
+        <v>212</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>38</v>
+        <v>340</v>
       </c>
       <c r="B110" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="B111" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="B112" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="B113" t="s">
-        <v>291</v>
+        <v>208</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="B114" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>13</v>
+        <v>340</v>
       </c>
       <c r="B115" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="B116" t="s">
-        <v>297</v>
+        <v>69</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>38</v>
+        <v>340</v>
       </c>
       <c r="B117" t="s">
-        <v>298</v>
+        <v>68</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>38</v>
+        <v>340</v>
       </c>
       <c r="B118" t="s">
-        <v>309</v>
+        <v>70</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>38</v>
+        <v>340</v>
       </c>
       <c r="B119" t="s">
-        <v>310</v>
+        <v>71</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>38</v>
+        <v>340</v>
       </c>
       <c r="B120" t="s">
-        <v>311</v>
+        <v>72</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
@@ -2389,15 +2423,15 @@
         <v>340</v>
       </c>
       <c r="B121" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B122" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
@@ -2405,7 +2439,7 @@
         <v>65</v>
       </c>
       <c r="B123" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
@@ -2413,7 +2447,7 @@
         <v>65</v>
       </c>
       <c r="B124" t="s">
-        <v>212</v>
+        <v>76</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
@@ -2421,23 +2455,23 @@
         <v>340</v>
       </c>
       <c r="B125" t="s">
-        <v>270</v>
+        <v>77</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B126" t="s">
-        <v>268</v>
+        <v>78</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B127" t="s">
-        <v>269</v>
+        <v>79</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
@@ -2445,15 +2479,15 @@
         <v>65</v>
       </c>
       <c r="B128" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B129" t="s">
-        <v>271</v>
+        <v>312</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
@@ -2461,15 +2495,15 @@
         <v>340</v>
       </c>
       <c r="B130" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B131" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
@@ -2477,15 +2511,15 @@
         <v>340</v>
       </c>
       <c r="B132" t="s">
-        <v>68</v>
+        <v>313</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B133" t="s">
-        <v>70</v>
+        <v>272</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
@@ -2493,7 +2527,7 @@
         <v>340</v>
       </c>
       <c r="B134" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
@@ -2501,47 +2535,47 @@
         <v>340</v>
       </c>
       <c r="B135" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B136" t="s">
-        <v>73</v>
+        <v>213</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B137" t="s">
-        <v>74</v>
+        <v>214</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B138" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B139" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B140" t="s">
-        <v>77</v>
+        <v>314</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
@@ -2549,7 +2583,7 @@
         <v>340</v>
       </c>
       <c r="B141" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
@@ -2557,7 +2591,7 @@
         <v>340</v>
       </c>
       <c r="B142" t="s">
-        <v>79</v>
+        <v>273</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
@@ -2565,23 +2599,23 @@
         <v>65</v>
       </c>
       <c r="B143" t="s">
-        <v>199</v>
+        <v>87</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B144" t="s">
-        <v>312</v>
+        <v>274</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B145" t="s">
-        <v>308</v>
+        <v>88</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
@@ -2589,7 +2623,7 @@
         <v>340</v>
       </c>
       <c r="B146" t="s">
-        <v>80</v>
+        <v>200</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
@@ -2597,15 +2631,15 @@
         <v>340</v>
       </c>
       <c r="B147" t="s">
-        <v>313</v>
+        <v>89</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B148" t="s">
-        <v>272</v>
+        <v>90</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
@@ -2613,7 +2647,7 @@
         <v>340</v>
       </c>
       <c r="B149" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
@@ -2621,15 +2655,15 @@
         <v>340</v>
       </c>
       <c r="B150" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B151" t="s">
-        <v>213</v>
+        <v>93</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
@@ -2637,31 +2671,31 @@
         <v>65</v>
       </c>
       <c r="B152" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B153" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B154" t="s">
-        <v>85</v>
+        <v>315</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B155" t="s">
-        <v>314</v>
+        <v>94</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
@@ -2669,7 +2703,7 @@
         <v>340</v>
       </c>
       <c r="B156" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
@@ -2677,31 +2711,31 @@
         <v>340</v>
       </c>
       <c r="B157" t="s">
-        <v>273</v>
+        <v>96</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B158" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B159" t="s">
-        <v>274</v>
+        <v>98</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B160" t="s">
-        <v>88</v>
+        <v>205</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
@@ -2709,7 +2743,7 @@
         <v>340</v>
       </c>
       <c r="B161" t="s">
-        <v>200</v>
+        <v>304</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
@@ -2717,7 +2751,7 @@
         <v>340</v>
       </c>
       <c r="B162" t="s">
-        <v>89</v>
+        <v>306</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
@@ -2725,7 +2759,7 @@
         <v>340</v>
       </c>
       <c r="B163" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
@@ -2733,15 +2767,15 @@
         <v>340</v>
       </c>
       <c r="B164" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B165" t="s">
-        <v>92</v>
+        <v>316</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
@@ -2749,31 +2783,31 @@
         <v>340</v>
       </c>
       <c r="B166" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B167" t="s">
-        <v>201</v>
+        <v>102</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B168" t="s">
-        <v>215</v>
+        <v>103</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B169" t="s">
-        <v>315</v>
+        <v>104</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
@@ -2781,7 +2815,7 @@
         <v>340</v>
       </c>
       <c r="B170" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
@@ -2789,7 +2823,7 @@
         <v>340</v>
       </c>
       <c r="B171" t="s">
-        <v>95</v>
+        <v>317</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
@@ -2797,7 +2831,7 @@
         <v>340</v>
       </c>
       <c r="B172" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
@@ -2805,31 +2839,31 @@
         <v>340</v>
       </c>
       <c r="B173" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B174" t="s">
-        <v>98</v>
+        <v>216</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B175" t="s">
-        <v>205</v>
+        <v>108</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B176" t="s">
-        <v>304</v>
+        <v>109</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
@@ -2837,7 +2871,7 @@
         <v>340</v>
       </c>
       <c r="B177" t="s">
-        <v>306</v>
+        <v>110</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
@@ -2845,7 +2879,7 @@
         <v>340</v>
       </c>
       <c r="B178" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
@@ -2853,23 +2887,23 @@
         <v>340</v>
       </c>
       <c r="B179" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B180" t="s">
-        <v>316</v>
+        <v>113</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B181" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
@@ -2877,39 +2911,39 @@
         <v>340</v>
       </c>
       <c r="B182" t="s">
-        <v>102</v>
+        <v>318</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B183" t="s">
-        <v>103</v>
+        <v>292</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B184" t="s">
-        <v>104</v>
+        <v>190</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B185" t="s">
-        <v>105</v>
+        <v>249</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B186" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
@@ -2917,7 +2951,7 @@
         <v>340</v>
       </c>
       <c r="B187" t="s">
-        <v>106</v>
+        <v>320</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
@@ -2925,31 +2959,31 @@
         <v>340</v>
       </c>
       <c r="B188" t="s">
-        <v>107</v>
+        <v>260</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B189" t="s">
-        <v>216</v>
+        <v>301</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B190" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B191" t="s">
-        <v>109</v>
+        <v>296</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
@@ -2957,7 +2991,7 @@
         <v>340</v>
       </c>
       <c r="B192" t="s">
-        <v>110</v>
+        <v>193</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
@@ -2965,23 +2999,23 @@
         <v>340</v>
       </c>
       <c r="B193" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B194" t="s">
-        <v>112</v>
+        <v>188</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B195" t="s">
-        <v>113</v>
+        <v>189</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
@@ -2989,15 +3023,15 @@
         <v>65</v>
       </c>
       <c r="B196" t="s">
-        <v>114</v>
+        <v>321</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B197" t="s">
-        <v>318</v>
+        <v>228</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
@@ -3005,7 +3039,7 @@
         <v>65</v>
       </c>
       <c r="B198" t="s">
-        <v>292</v>
+        <v>202</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
@@ -3013,39 +3047,39 @@
         <v>65</v>
       </c>
       <c r="B199" t="s">
-        <v>190</v>
+        <v>117</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B200" t="s">
-        <v>249</v>
+        <v>322</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B201" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B202" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B203" t="s">
-        <v>260</v>
+        <v>217</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
@@ -3053,7 +3087,7 @@
         <v>340</v>
       </c>
       <c r="B204" t="s">
-        <v>301</v>
+        <v>118</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
@@ -3061,23 +3095,23 @@
         <v>340</v>
       </c>
       <c r="B205" t="s">
-        <v>115</v>
+        <v>293</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B206" t="s">
-        <v>296</v>
+        <v>119</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B207" t="s">
-        <v>193</v>
+        <v>120</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
@@ -3085,7 +3119,7 @@
         <v>340</v>
       </c>
       <c r="B208" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
@@ -3093,7 +3127,7 @@
         <v>65</v>
       </c>
       <c r="B209" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
@@ -3101,7 +3135,7 @@
         <v>65</v>
       </c>
       <c r="B210" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
@@ -3109,7 +3143,7 @@
         <v>65</v>
       </c>
       <c r="B211" t="s">
-        <v>321</v>
+        <v>229</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
@@ -3117,23 +3151,23 @@
         <v>65</v>
       </c>
       <c r="B212" t="s">
-        <v>228</v>
+        <v>288</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B213" t="s">
-        <v>202</v>
+        <v>122</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B214" t="s">
-        <v>117</v>
+        <v>276</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
@@ -3141,7 +3175,7 @@
         <v>340</v>
       </c>
       <c r="B215" t="s">
-        <v>322</v>
+        <v>123</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
@@ -3149,7 +3183,7 @@
         <v>340</v>
       </c>
       <c r="B216" t="s">
-        <v>303</v>
+        <v>124</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
@@ -3157,47 +3191,47 @@
         <v>65</v>
       </c>
       <c r="B217" t="s">
-        <v>323</v>
+        <v>126</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B218" t="s">
-        <v>217</v>
+        <v>125</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B219" t="s">
-        <v>118</v>
+        <v>230</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B220" t="s">
-        <v>293</v>
+        <v>219</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B221" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B222" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
@@ -3205,47 +3239,47 @@
         <v>340</v>
       </c>
       <c r="B223" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B224" t="s">
-        <v>203</v>
+        <v>130</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B225" t="s">
-        <v>209</v>
+        <v>131</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B226" t="s">
-        <v>229</v>
+        <v>132</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B227" t="s">
-        <v>288</v>
+        <v>133</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B228" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
@@ -3253,15 +3287,15 @@
         <v>340</v>
       </c>
       <c r="B229" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B230" t="s">
-        <v>123</v>
+        <v>227</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
@@ -3269,7 +3303,7 @@
         <v>340</v>
       </c>
       <c r="B231" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
@@ -3277,7 +3311,7 @@
         <v>65</v>
       </c>
       <c r="B232" t="s">
-        <v>126</v>
+        <v>324</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
@@ -3285,23 +3319,23 @@
         <v>340</v>
       </c>
       <c r="B233" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B234" t="s">
-        <v>230</v>
+        <v>138</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B235" t="s">
-        <v>219</v>
+        <v>139</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
@@ -3309,7 +3343,7 @@
         <v>340</v>
       </c>
       <c r="B236" t="s">
-        <v>127</v>
+        <v>325</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
@@ -3317,7 +3351,7 @@
         <v>340</v>
       </c>
       <c r="B237" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
@@ -3325,7 +3359,7 @@
         <v>340</v>
       </c>
       <c r="B238" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
@@ -3333,7 +3367,7 @@
         <v>340</v>
       </c>
       <c r="B239" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
@@ -3341,15 +3375,15 @@
         <v>340</v>
       </c>
       <c r="B240" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B241" t="s">
-        <v>132</v>
+        <v>326</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
@@ -3357,15 +3391,15 @@
         <v>340</v>
       </c>
       <c r="B242" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B243" t="s">
-        <v>134</v>
+        <v>327</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
@@ -3373,15 +3407,15 @@
         <v>340</v>
       </c>
       <c r="B244" t="s">
-        <v>277</v>
+        <v>145</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B245" t="s">
-        <v>227</v>
+        <v>146</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
@@ -3389,15 +3423,15 @@
         <v>340</v>
       </c>
       <c r="B246" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B247" t="s">
-        <v>324</v>
+        <v>148</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
@@ -3405,7 +3439,7 @@
         <v>340</v>
       </c>
       <c r="B248" t="s">
-        <v>137</v>
+        <v>328</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
@@ -3413,23 +3447,23 @@
         <v>340</v>
       </c>
       <c r="B249" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B250" t="s">
-        <v>139</v>
+        <v>220</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B251" t="s">
-        <v>325</v>
+        <v>226</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
@@ -3437,7 +3471,7 @@
         <v>340</v>
       </c>
       <c r="B252" t="s">
-        <v>140</v>
+        <v>278</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
@@ -3445,23 +3479,23 @@
         <v>340</v>
       </c>
       <c r="B253" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B254" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B255" t="s">
-        <v>143</v>
+        <v>289</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
@@ -3469,15 +3503,15 @@
         <v>65</v>
       </c>
       <c r="B256" t="s">
-        <v>326</v>
+        <v>279</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B257" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
@@ -3485,7 +3519,7 @@
         <v>340</v>
       </c>
       <c r="B258" t="s">
-        <v>327</v>
+        <v>153</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
@@ -3493,7 +3527,7 @@
         <v>340</v>
       </c>
       <c r="B259" t="s">
-        <v>145</v>
+        <v>302</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
@@ -3501,23 +3535,23 @@
         <v>340</v>
       </c>
       <c r="B260" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B261" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B262" t="s">
-        <v>148</v>
+        <v>246</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
@@ -3525,7 +3559,7 @@
         <v>340</v>
       </c>
       <c r="B263" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
@@ -3533,7 +3567,7 @@
         <v>340</v>
       </c>
       <c r="B264" t="s">
-        <v>149</v>
+        <v>251</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
@@ -3541,7 +3575,7 @@
         <v>65</v>
       </c>
       <c r="B265" t="s">
-        <v>220</v>
+        <v>280</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
@@ -3549,15 +3583,15 @@
         <v>65</v>
       </c>
       <c r="B266" t="s">
-        <v>226</v>
+        <v>329</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B267" t="s">
-        <v>278</v>
+        <v>330</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
@@ -3565,47 +3599,47 @@
         <v>340</v>
       </c>
       <c r="B268" t="s">
-        <v>150</v>
+        <v>206</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B269" t="s">
-        <v>151</v>
+        <v>198</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B270" t="s">
-        <v>289</v>
+        <v>156</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B271" t="s">
-        <v>279</v>
+        <v>331</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B272" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B273" t="s">
-        <v>153</v>
+        <v>281</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
@@ -3613,7 +3647,7 @@
         <v>340</v>
       </c>
       <c r="B274" t="s">
-        <v>302</v>
+        <v>158</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
@@ -3621,23 +3655,23 @@
         <v>340</v>
       </c>
       <c r="B275" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B276" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B277" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
@@ -3645,7 +3679,7 @@
         <v>340</v>
       </c>
       <c r="B278" t="s">
-        <v>299</v>
+        <v>332</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
@@ -3653,31 +3687,31 @@
         <v>340</v>
       </c>
       <c r="B279" t="s">
-        <v>251</v>
+        <v>161</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B280" t="s">
-        <v>280</v>
+        <v>162</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B281" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B282" t="s">
-        <v>330</v>
+        <v>163</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
@@ -3685,7 +3719,7 @@
         <v>340</v>
       </c>
       <c r="B283" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
@@ -3693,7 +3727,7 @@
         <v>340</v>
       </c>
       <c r="B284" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
@@ -3701,7 +3735,7 @@
         <v>340</v>
       </c>
       <c r="B285" t="s">
-        <v>156</v>
+        <v>334</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
@@ -3709,7 +3743,7 @@
         <v>340</v>
       </c>
       <c r="B286" t="s">
-        <v>331</v>
+        <v>166</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
@@ -3717,15 +3751,15 @@
         <v>340</v>
       </c>
       <c r="B287" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B288" t="s">
-        <v>281</v>
+        <v>167</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
@@ -3733,15 +3767,15 @@
         <v>340</v>
       </c>
       <c r="B289" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B290" t="s">
-        <v>159</v>
+        <v>335</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
@@ -3749,7 +3783,7 @@
         <v>340</v>
       </c>
       <c r="B291" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
@@ -3757,23 +3791,23 @@
         <v>340</v>
       </c>
       <c r="B292" t="s">
-        <v>259</v>
+        <v>170</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B293" t="s">
-        <v>332</v>
+        <v>282</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B294" t="s">
-        <v>161</v>
+        <v>204</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
@@ -3781,7 +3815,7 @@
         <v>340</v>
       </c>
       <c r="B295" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
@@ -3789,7 +3823,7 @@
         <v>340</v>
       </c>
       <c r="B296" t="s">
-        <v>333</v>
+        <v>283</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
@@ -3797,7 +3831,7 @@
         <v>340</v>
       </c>
       <c r="B297" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
@@ -3805,15 +3839,15 @@
         <v>340</v>
       </c>
       <c r="B298" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B299" t="s">
-        <v>165</v>
+        <v>290</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
@@ -3821,7 +3855,7 @@
         <v>340</v>
       </c>
       <c r="B300" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
@@ -3829,7 +3863,7 @@
         <v>340</v>
       </c>
       <c r="B301" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
@@ -3837,7 +3871,7 @@
         <v>340</v>
       </c>
       <c r="B302" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
@@ -3845,7 +3879,7 @@
         <v>340</v>
       </c>
       <c r="B303" t="s">
-        <v>167</v>
+        <v>286</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
@@ -3853,7 +3887,7 @@
         <v>340</v>
       </c>
       <c r="B304" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
@@ -3861,7 +3895,7 @@
         <v>65</v>
       </c>
       <c r="B305" t="s">
-        <v>335</v>
+        <v>221</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
@@ -3869,7 +3903,7 @@
         <v>340</v>
       </c>
       <c r="B306" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
@@ -3877,23 +3911,23 @@
         <v>340</v>
       </c>
       <c r="B307" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B308" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B309" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
@@ -3901,39 +3935,39 @@
         <v>340</v>
       </c>
       <c r="B310" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B311" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B312" t="s">
-        <v>173</v>
+        <v>211</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B313" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B314" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
@@ -3941,7 +3975,7 @@
         <v>340</v>
       </c>
       <c r="B315" t="s">
-        <v>336</v>
+        <v>300</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
@@ -3949,15 +3983,15 @@
         <v>340</v>
       </c>
       <c r="B316" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B317" t="s">
-        <v>176</v>
+        <v>222</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
@@ -3965,7 +3999,7 @@
         <v>340</v>
       </c>
       <c r="B318" t="s">
-        <v>286</v>
+        <v>182</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
@@ -3973,39 +4007,39 @@
         <v>340</v>
       </c>
       <c r="B319" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B320" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B321" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B322" t="s">
-        <v>178</v>
+        <v>224</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="B323" t="s">
-        <v>337</v>
+        <v>225</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
@@ -4013,7 +4047,7 @@
         <v>340</v>
       </c>
       <c r="B324" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
@@ -4021,31 +4055,31 @@
         <v>340</v>
       </c>
       <c r="B325" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B326" t="s">
-        <v>307</v>
+        <v>187</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B327" t="s">
-        <v>211</v>
+        <v>338</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B328" t="s">
-        <v>210</v>
+        <v>339</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
@@ -4053,7 +4087,7 @@
         <v>340</v>
       </c>
       <c r="B329" t="s">
-        <v>287</v>
+        <v>342</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
@@ -4061,7 +4095,7 @@
         <v>340</v>
       </c>
       <c r="B330" t="s">
-        <v>300</v>
+        <v>343</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
@@ -4069,15 +4103,15 @@
         <v>340</v>
       </c>
       <c r="B331" t="s">
-        <v>181</v>
+        <v>344</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="B332" t="s">
-        <v>222</v>
+        <v>345</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
@@ -4085,90 +4119,13 @@
         <v>340</v>
       </c>
       <c r="B333" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A334" t="s">
-        <v>340</v>
-      </c>
-      <c r="B334" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A335" t="s">
-        <v>340</v>
-      </c>
-      <c r="B335" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A336" t="s">
-        <v>65</v>
-      </c>
-      <c r="B336" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A337" t="s">
-        <v>65</v>
-      </c>
-      <c r="B337" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A338" t="s">
-        <v>65</v>
-      </c>
-      <c r="B338" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A339" t="s">
-        <v>340</v>
-      </c>
-      <c r="B339" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A340" t="s">
-        <v>340</v>
-      </c>
-      <c r="B340" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A341" t="s">
-        <v>340</v>
-      </c>
-      <c r="B341" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A342" t="s">
-        <v>340</v>
-      </c>
-      <c r="B342" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A343" t="s">
-        <v>340</v>
-      </c>
-      <c r="B343" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Master/DATABASE_IA.xlsx
+++ b/Master/DATABASE_IA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FORMAT DAN TEMPLATE\T013_Vba_Spit_data\DEX\Master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4658E21C-4B82-47E2-9800-6B957DC307F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6EDDDA-F2DA-42E9-901C-3C7B5B604385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{69F88D26-E53E-44EB-8F6B-6F72C75FF8C3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{69F88D26-E53E-44EB-8F6B-6F72C75FF8C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,23 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="355">
   <si>
     <t>10.FOOD [BUMBU] - COM V.2</t>
   </si>
@@ -1080,6 +1069,30 @@
   </si>
   <si>
     <t>SENDOK TAKAR STAINLESS SET</t>
+  </si>
+  <si>
+    <t>LPG 50KG</t>
+  </si>
+  <si>
+    <t>TERMOMETER DIGITAL</t>
+  </si>
+  <si>
+    <t>TERMOMETER WATERPROF JOIL KT 1</t>
+  </si>
+  <si>
+    <t>PISAU GILING DAGING TJ 8</t>
+  </si>
+  <si>
+    <t>TERMOGUN 50 600 C PRO</t>
+  </si>
+  <si>
+    <t>DUSTBIN 60 LITER</t>
+  </si>
+  <si>
+    <t>KESET ANTI SLIP</t>
+  </si>
+  <si>
+    <t>PANCI KUKUS CABE UK 36</t>
   </si>
 </sst>
 </file>
@@ -1115,13 +1128,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1129,14 +1145,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1154,9 +1162,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1194,7 +1202,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1300,7 +1308,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1442,7 +1450,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1451,14 +1459,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08B8BE52-5B4F-47C1-84A8-24A4E0133727}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B333"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B341"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -1466,7 +1474,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1474,7 +1482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1482,7 +1490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1490,7 +1498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1498,7 +1506,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1506,7 +1514,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1514,7 +1522,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1522,7 +1530,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1530,7 +1538,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>341</v>
       </c>
@@ -1538,7 +1546,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>341</v>
       </c>
@@ -1546,7 +1554,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>341</v>
       </c>
@@ -1554,7 +1562,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>341</v>
       </c>
@@ -1562,7 +1570,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>341</v>
       </c>
@@ -1570,7 +1578,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>341</v>
       </c>
@@ -1578,7 +1586,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>341</v>
       </c>
@@ -1586,7 +1594,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>341</v>
       </c>
@@ -1594,7 +1602,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>341</v>
       </c>
@@ -1602,7 +1610,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>341</v>
       </c>
@@ -1610,7 +1618,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>341</v>
       </c>
@@ -1618,7 +1626,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>341</v>
       </c>
@@ -1626,7 +1634,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>341</v>
       </c>
@@ -1634,7 +1642,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>341</v>
       </c>
@@ -1642,7 +1650,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>341</v>
       </c>
@@ -1650,7 +1658,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -1658,7 +1666,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>13</v>
       </c>
@@ -1666,7 +1674,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -1674,7 +1682,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>13</v>
       </c>
@@ -1682,7 +1690,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -1690,7 +1698,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>13</v>
       </c>
@@ -1698,7 +1706,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -1706,7 +1714,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>13</v>
       </c>
@@ -1714,7 +1722,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>13</v>
       </c>
@@ -1722,7 +1730,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>13</v>
       </c>
@@ -1730,7 +1738,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -1738,7 +1746,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>13</v>
       </c>
@@ -1746,7 +1754,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>34</v>
       </c>
@@ -1754,7 +1762,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>13</v>
       </c>
@@ -1762,7 +1770,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -1770,7 +1778,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -1778,7 +1786,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>38</v>
       </c>
@@ -1786,7 +1794,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>38</v>
       </c>
@@ -1794,7 +1802,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>38</v>
       </c>
@@ -1802,7 +1810,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>38</v>
       </c>
@@ -1810,7 +1818,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>38</v>
       </c>
@@ -1818,7 +1826,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>38</v>
       </c>
@@ -1826,7 +1834,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>38</v>
       </c>
@@ -1834,7 +1842,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>38</v>
       </c>
@@ -1842,7 +1850,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>38</v>
       </c>
@@ -1850,7 +1858,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>38</v>
       </c>
@@ -1858,7 +1866,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>38</v>
       </c>
@@ -1866,7 +1874,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>38</v>
       </c>
@@ -1874,7 +1882,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>38</v>
       </c>
@@ -1882,7 +1890,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>38</v>
       </c>
@@ -1890,7 +1898,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>38</v>
       </c>
@@ -1898,7 +1906,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>38</v>
       </c>
@@ -1906,7 +1914,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>38</v>
       </c>
@@ -1914,7 +1922,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>38</v>
       </c>
@@ -1922,7 +1930,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>38</v>
       </c>
@@ -1930,7 +1938,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>38</v>
       </c>
@@ -1938,7 +1946,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>38</v>
       </c>
@@ -1946,7 +1954,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>38</v>
       </c>
@@ -1954,7 +1962,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>63</v>
       </c>
@@ -1962,7 +1970,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>38</v>
       </c>
@@ -1970,7 +1978,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -1978,7 +1986,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>63</v>
       </c>
@@ -1986,7 +1994,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>38</v>
       </c>
@@ -1994,7 +2002,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>13</v>
       </c>
@@ -2002,7 +2010,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>13</v>
       </c>
@@ -2010,7 +2018,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>38</v>
       </c>
@@ -2018,7 +2026,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>232</v>
       </c>
@@ -2026,7 +2034,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>232</v>
       </c>
@@ -2034,7 +2042,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>232</v>
       </c>
@@ -2042,7 +2050,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>232</v>
       </c>
@@ -2050,7 +2058,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>232</v>
       </c>
@@ -2058,7 +2066,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>232</v>
       </c>
@@ -2066,7 +2074,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>232</v>
       </c>
@@ -2074,7 +2082,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>232</v>
       </c>
@@ -2082,7 +2090,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>232</v>
       </c>
@@ -2090,7 +2098,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>232</v>
       </c>
@@ -2098,7 +2106,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>232</v>
       </c>
@@ -2106,7 +2114,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>232</v>
       </c>
@@ -2114,7 +2122,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>245</v>
       </c>
@@ -2122,7 +2130,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>232</v>
       </c>
@@ -2130,7 +2138,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>13</v>
       </c>
@@ -2138,7 +2146,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>13</v>
       </c>
@@ -2146,7 +2154,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>13</v>
       </c>
@@ -2154,7 +2162,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>13</v>
       </c>
@@ -2162,7 +2170,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>232</v>
       </c>
@@ -2170,7 +2178,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>13</v>
       </c>
@@ -2178,7 +2186,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>13</v>
       </c>
@@ -2186,7 +2194,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>34</v>
       </c>
@@ -2194,7 +2202,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>13</v>
       </c>
@@ -2202,7 +2210,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>257</v>
       </c>
@@ -2210,7 +2218,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>38</v>
       </c>
@@ -2218,7 +2226,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>63</v>
       </c>
@@ -2226,7 +2234,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>38</v>
       </c>
@@ -2234,7 +2242,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>38</v>
       </c>
@@ -2242,7 +2250,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>38</v>
       </c>
@@ -2250,7 +2258,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>38</v>
       </c>
@@ -2258,7 +2266,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>38</v>
       </c>
@@ -2266,7 +2274,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>38</v>
       </c>
@@ -2274,7 +2282,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>38</v>
       </c>
@@ -2282,7 +2290,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>38</v>
       </c>
@@ -2290,7 +2298,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>38</v>
       </c>
@@ -2298,7 +2306,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>340</v>
       </c>
@@ -2306,7 +2314,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>65</v>
       </c>
@@ -2314,7 +2322,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>65</v>
       </c>
@@ -2322,7 +2330,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>65</v>
       </c>
@@ -2330,7 +2338,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>340</v>
       </c>
@@ -2338,7 +2346,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>65</v>
       </c>
@@ -2346,7 +2354,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>65</v>
       </c>
@@ -2354,7 +2362,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>65</v>
       </c>
@@ -2362,7 +2370,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>65</v>
       </c>
@@ -2370,7 +2378,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>340</v>
       </c>
@@ -2378,7 +2386,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>65</v>
       </c>
@@ -2386,7 +2394,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>340</v>
       </c>
@@ -2394,7 +2402,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>340</v>
       </c>
@@ -2402,7 +2410,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>340</v>
       </c>
@@ -2410,7 +2418,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>340</v>
       </c>
@@ -2418,7 +2426,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>340</v>
       </c>
@@ -2426,7 +2434,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>340</v>
       </c>
@@ -2434,7 +2442,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>65</v>
       </c>
@@ -2442,7 +2450,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>65</v>
       </c>
@@ -2450,7 +2458,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>340</v>
       </c>
@@ -2458,7 +2466,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>340</v>
       </c>
@@ -2466,7 +2474,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>340</v>
       </c>
@@ -2474,7 +2482,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>65</v>
       </c>
@@ -2482,7 +2490,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>340</v>
       </c>
@@ -2490,7 +2498,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>340</v>
       </c>
@@ -2498,7 +2506,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>340</v>
       </c>
@@ -2506,7 +2514,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>340</v>
       </c>
@@ -2514,7 +2522,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>65</v>
       </c>
@@ -2522,7 +2530,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>340</v>
       </c>
@@ -2530,7 +2538,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>340</v>
       </c>
@@ -2538,7 +2546,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>65</v>
       </c>
@@ -2546,7 +2554,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>65</v>
       </c>
@@ -2554,7 +2562,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>340</v>
       </c>
@@ -2562,7 +2570,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>340</v>
       </c>
@@ -2570,7 +2578,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>65</v>
       </c>
@@ -2578,7 +2586,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>340</v>
       </c>
@@ -2586,7 +2594,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>340</v>
       </c>
@@ -2594,7 +2602,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>65</v>
       </c>
@@ -2602,7 +2610,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>65</v>
       </c>
@@ -2610,7 +2618,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>65</v>
       </c>
@@ -2618,7 +2626,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>340</v>
       </c>
@@ -2626,7 +2634,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>340</v>
       </c>
@@ -2634,7 +2642,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>340</v>
       </c>
@@ -2642,7 +2650,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>340</v>
       </c>
@@ -2650,7 +2658,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>340</v>
       </c>
@@ -2658,7 +2666,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>340</v>
       </c>
@@ -2666,7 +2674,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>65</v>
       </c>
@@ -2674,7 +2682,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>65</v>
       </c>
@@ -2682,7 +2690,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>65</v>
       </c>
@@ -2690,7 +2698,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>340</v>
       </c>
@@ -2698,7 +2706,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>340</v>
       </c>
@@ -2706,7 +2714,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>340</v>
       </c>
@@ -2714,7 +2722,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>340</v>
       </c>
@@ -2722,7 +2730,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>340</v>
       </c>
@@ -2730,7 +2738,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>340</v>
       </c>
@@ -2738,7 +2746,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>340</v>
       </c>
@@ -2746,7 +2754,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>340</v>
       </c>
@@ -2754,7 +2762,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>340</v>
       </c>
@@ -2762,7 +2770,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>340</v>
       </c>
@@ -2770,7 +2778,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>65</v>
       </c>
@@ -2778,7 +2786,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>340</v>
       </c>
@@ -2786,7 +2794,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>340</v>
       </c>
@@ -2794,7 +2802,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>340</v>
       </c>
@@ -2802,7 +2810,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>340</v>
       </c>
@@ -2810,7 +2818,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>340</v>
       </c>
@@ -2818,7 +2826,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>340</v>
       </c>
@@ -2826,7 +2834,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>340</v>
       </c>
@@ -2834,7 +2842,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>340</v>
       </c>
@@ -2842,7 +2850,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>65</v>
       </c>
@@ -2850,7 +2858,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>65</v>
       </c>
@@ -2858,7 +2866,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>65</v>
       </c>
@@ -2866,7 +2874,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>340</v>
       </c>
@@ -2874,7 +2882,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>340</v>
       </c>
@@ -2882,7 +2890,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>340</v>
       </c>
@@ -2890,7 +2898,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>340</v>
       </c>
@@ -2898,7 +2906,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>65</v>
       </c>
@@ -2906,7 +2914,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>340</v>
       </c>
@@ -2914,7 +2922,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>65</v>
       </c>
@@ -2922,7 +2930,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>65</v>
       </c>
@@ -2930,7 +2938,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>65</v>
       </c>
@@ -2938,7 +2946,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>65</v>
       </c>
@@ -2946,7 +2954,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>340</v>
       </c>
@@ -2954,7 +2962,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>340</v>
       </c>
@@ -2962,7 +2970,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>340</v>
       </c>
@@ -2970,7 +2978,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>340</v>
       </c>
@@ -2978,7 +2986,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>340</v>
       </c>
@@ -2986,7 +2994,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>340</v>
       </c>
@@ -2994,7 +3002,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>340</v>
       </c>
@@ -3002,7 +3010,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>65</v>
       </c>
@@ -3010,7 +3018,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>65</v>
       </c>
@@ -3018,7 +3026,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>65</v>
       </c>
@@ -3026,7 +3034,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>65</v>
       </c>
@@ -3034,7 +3042,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>65</v>
       </c>
@@ -3042,7 +3050,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>65</v>
       </c>
@@ -3050,7 +3058,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>340</v>
       </c>
@@ -3058,7 +3066,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>340</v>
       </c>
@@ -3066,7 +3074,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>65</v>
       </c>
@@ -3074,7 +3082,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>65</v>
       </c>
@@ -3082,7 +3090,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>340</v>
       </c>
@@ -3090,7 +3098,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>340</v>
       </c>
@@ -3098,7 +3106,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>65</v>
       </c>
@@ -3106,7 +3114,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>65</v>
       </c>
@@ -3114,7 +3122,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>340</v>
       </c>
@@ -3122,7 +3130,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>65</v>
       </c>
@@ -3130,7 +3138,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>65</v>
       </c>
@@ -3138,7 +3146,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>65</v>
       </c>
@@ -3146,7 +3154,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>65</v>
       </c>
@@ -3154,7 +3162,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>340</v>
       </c>
@@ -3162,7 +3170,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>340</v>
       </c>
@@ -3170,7 +3178,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>340</v>
       </c>
@@ -3178,7 +3186,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>340</v>
       </c>
@@ -3186,7 +3194,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>65</v>
       </c>
@@ -3194,7 +3202,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>340</v>
       </c>
@@ -3202,7 +3210,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>65</v>
       </c>
@@ -3210,7 +3218,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>65</v>
       </c>
@@ -3218,7 +3226,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>340</v>
       </c>
@@ -3226,7 +3234,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>340</v>
       </c>
@@ -3234,7 +3242,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>340</v>
       </c>
@@ -3242,7 +3250,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>340</v>
       </c>
@@ -3250,7 +3258,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>340</v>
       </c>
@@ -3258,7 +3266,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>340</v>
       </c>
@@ -3266,7 +3274,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>340</v>
       </c>
@@ -3274,7 +3282,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>65</v>
       </c>
@@ -3282,7 +3290,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>340</v>
       </c>
@@ -3290,7 +3298,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>65</v>
       </c>
@@ -3298,7 +3306,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>340</v>
       </c>
@@ -3306,7 +3314,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>65</v>
       </c>
@@ -3314,7 +3322,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>340</v>
       </c>
@@ -3322,7 +3330,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>340</v>
       </c>
@@ -3330,7 +3338,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>340</v>
       </c>
@@ -3338,7 +3346,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>340</v>
       </c>
@@ -3346,7 +3354,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>340</v>
       </c>
@@ -3354,7 +3362,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>340</v>
       </c>
@@ -3362,7 +3370,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>340</v>
       </c>
@@ -3370,7 +3378,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>340</v>
       </c>
@@ -3378,7 +3386,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>65</v>
       </c>
@@ -3386,7 +3394,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>340</v>
       </c>
@@ -3394,7 +3402,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>340</v>
       </c>
@@ -3402,7 +3410,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>340</v>
       </c>
@@ -3410,7 +3418,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>340</v>
       </c>
@@ -3418,7 +3426,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>340</v>
       </c>
@@ -3426,7 +3434,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>340</v>
       </c>
@@ -3434,7 +3442,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>340</v>
       </c>
@@ -3442,7 +3450,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>340</v>
       </c>
@@ -3450,7 +3458,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>65</v>
       </c>
@@ -3458,7 +3466,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>65</v>
       </c>
@@ -3466,7 +3474,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>340</v>
       </c>
@@ -3474,7 +3482,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>340</v>
       </c>
@@ -3482,7 +3490,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>65</v>
       </c>
@@ -3490,7 +3498,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>65</v>
       </c>
@@ -3498,7 +3506,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>65</v>
       </c>
@@ -3506,7 +3514,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>65</v>
       </c>
@@ -3514,7 +3522,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>340</v>
       </c>
@@ -3522,7 +3530,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>340</v>
       </c>
@@ -3530,7 +3538,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>340</v>
       </c>
@@ -3538,7 +3546,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>65</v>
       </c>
@@ -3546,7 +3554,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>65</v>
       </c>
@@ -3554,7 +3562,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>340</v>
       </c>
@@ -3562,7 +3570,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>340</v>
       </c>
@@ -3570,7 +3578,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>65</v>
       </c>
@@ -3578,7 +3586,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>65</v>
       </c>
@@ -3586,7 +3594,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>65</v>
       </c>
@@ -3594,7 +3602,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>340</v>
       </c>
@@ -3602,7 +3610,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>340</v>
       </c>
@@ -3610,7 +3618,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>340</v>
       </c>
@@ -3618,7 +3626,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>340</v>
       </c>
@@ -3626,7 +3634,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>340</v>
       </c>
@@ -3634,7 +3642,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>65</v>
       </c>
@@ -3642,7 +3650,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>340</v>
       </c>
@@ -3650,7 +3658,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>340</v>
       </c>
@@ -3658,7 +3666,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>340</v>
       </c>
@@ -3666,7 +3674,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>340</v>
       </c>
@@ -3674,7 +3682,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>340</v>
       </c>
@@ -3682,7 +3690,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>340</v>
       </c>
@@ -3690,7 +3698,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>340</v>
       </c>
@@ -3698,7 +3706,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>340</v>
       </c>
@@ -3706,7 +3714,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>340</v>
       </c>
@@ -3714,7 +3722,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>340</v>
       </c>
@@ -3722,7 +3730,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>340</v>
       </c>
@@ -3730,7 +3738,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>340</v>
       </c>
@@ -3738,7 +3746,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>340</v>
       </c>
@@ -3746,7 +3754,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>340</v>
       </c>
@@ -3754,7 +3762,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>340</v>
       </c>
@@ -3762,7 +3770,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>340</v>
       </c>
@@ -3770,7 +3778,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>65</v>
       </c>
@@ -3778,7 +3786,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>340</v>
       </c>
@@ -3786,7 +3794,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>340</v>
       </c>
@@ -3794,7 +3802,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>65</v>
       </c>
@@ -3802,7 +3810,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>65</v>
       </c>
@@ -3810,7 +3818,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>340</v>
       </c>
@@ -3818,7 +3826,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>340</v>
       </c>
@@ -3826,7 +3834,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>340</v>
       </c>
@@ -3834,7 +3842,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>340</v>
       </c>
@@ -3842,7 +3850,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>65</v>
       </c>
@@ -3850,7 +3858,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>340</v>
       </c>
@@ -3858,7 +3866,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>340</v>
       </c>
@@ -3866,7 +3874,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>340</v>
       </c>
@@ -3874,7 +3882,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>340</v>
       </c>
@@ -3882,7 +3890,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>340</v>
       </c>
@@ -3890,7 +3898,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>65</v>
       </c>
@@ -3898,7 +3906,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>340</v>
       </c>
@@ -3906,7 +3914,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>340</v>
       </c>
@@ -3914,7 +3922,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>340</v>
       </c>
@@ -3922,7 +3930,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>340</v>
       </c>
@@ -3930,7 +3938,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>340</v>
       </c>
@@ -3938,7 +3946,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>65</v>
       </c>
@@ -3946,7 +3954,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>65</v>
       </c>
@@ -3954,7 +3962,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>65</v>
       </c>
@@ -3962,7 +3970,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>340</v>
       </c>
@@ -3970,7 +3978,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>340</v>
       </c>
@@ -3978,7 +3986,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>340</v>
       </c>
@@ -3986,7 +3994,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>65</v>
       </c>
@@ -3994,7 +4002,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>340</v>
       </c>
@@ -4002,7 +4010,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>340</v>
       </c>
@@ -4010,7 +4018,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>340</v>
       </c>
@@ -4018,7 +4026,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>65</v>
       </c>
@@ -4026,7 +4034,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>65</v>
       </c>
@@ -4034,7 +4042,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>65</v>
       </c>
@@ -4042,7 +4050,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>340</v>
       </c>
@@ -4050,7 +4058,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>340</v>
       </c>
@@ -4058,7 +4066,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>340</v>
       </c>
@@ -4066,7 +4074,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>340</v>
       </c>
@@ -4074,7 +4082,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>340</v>
       </c>
@@ -4082,7 +4090,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>340</v>
       </c>
@@ -4090,7 +4098,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>340</v>
       </c>
@@ -4098,7 +4106,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>340</v>
       </c>
@@ -4106,7 +4114,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>340</v>
       </c>
@@ -4114,12 +4122,76 @@
         <v>345</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>340</v>
       </c>
       <c r="B333" t="s">
         <v>346</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>245</v>
+      </c>
+      <c r="B334" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A335" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B335" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A336" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B336" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A337" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B337" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A338" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B338" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A339" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B339" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A340" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B340" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A341" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B341" t="s">
+        <v>354</v>
       </c>
     </row>
   </sheetData>

--- a/Master/DATABASE_IA.xlsx
+++ b/Master/DATABASE_IA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FORMAT DAN TEMPLATE\T013_Vba_Spit_data\DEX\Master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6EDDDA-F2DA-42E9-901C-3C7B5B604385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFB3884-AE27-42A8-BBF7-644FACADD726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{69F88D26-E53E-44EB-8F6B-6F72C75FF8C3}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$335</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$401</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="415">
   <si>
     <t>10.FOOD [BUMBU] - COM V.2</t>
   </si>
@@ -1093,6 +1093,186 @@
   </si>
   <si>
     <t>PANCI KUKUS CABE UK 36</t>
+  </si>
+  <si>
+    <t>APRON CREW BAKSO</t>
+  </si>
+  <si>
+    <t>ARANG BAKARAN</t>
+  </si>
+  <si>
+    <t>BUN PAN UK. 400X600X30 MM</t>
+  </si>
+  <si>
+    <t>BUN PAN UK. 457X660X50 MM</t>
+  </si>
+  <si>
+    <t>CAIRAN FORCEMAXX</t>
+  </si>
+  <si>
+    <t>CAPIT SILICON SEDANG</t>
+  </si>
+  <si>
+    <t>CELANA LEADER BAKSO</t>
+  </si>
+  <si>
+    <t>CENTONG KUAH PANJANG 40 CM</t>
+  </si>
+  <si>
+    <t>CENTONG LUBANG</t>
+  </si>
+  <si>
+    <t>CENTONG NASI BESAR</t>
+  </si>
+  <si>
+    <t>CERMIN GROOMING</t>
+  </si>
+  <si>
+    <t>COVER FOODPAN 1/1 - 100 MM</t>
+  </si>
+  <si>
+    <t>COVER FOODPAN 1/2 - 100 MM</t>
+  </si>
+  <si>
+    <t>COVER FOODPAN 1/4 - 100 MM</t>
+  </si>
+  <si>
+    <t>COVER FOODPAN 1/4 - 150 MM</t>
+  </si>
+  <si>
+    <t>COVER FOODPAN 1/9 - 100 MM</t>
+  </si>
+  <si>
+    <t>COVER FOODPAN LADLE 1/9 - 100 MM</t>
+  </si>
+  <si>
+    <t>CUP HOLDER 4 GRID</t>
+  </si>
+  <si>
+    <t>DIGITAL THERMOMETER FRYER</t>
+  </si>
+  <si>
+    <t>DISPENSER PEHARUM RUANGAN</t>
+  </si>
+  <si>
+    <t>DISPENSER SAUCE 4X3 LITER</t>
+  </si>
+  <si>
+    <t>FOODPAN 1/1 - 100 MM</t>
+  </si>
+  <si>
+    <t>FOODPAN 1/2 - 100 MM</t>
+  </si>
+  <si>
+    <t>FOODPAN 1/4 - 100 MM</t>
+  </si>
+  <si>
+    <t>FOODPAN 1/4 - 150 MM</t>
+  </si>
+  <si>
+    <t>FOODPAN 1/9 - 100 MM</t>
+  </si>
+  <si>
+    <t>FOODPAN 1/9 - 65 MM</t>
+  </si>
+  <si>
+    <t>GELAS TAKAR 200 ML</t>
+  </si>
+  <si>
+    <t>GUNTING STAINLESS</t>
+  </si>
+  <si>
+    <t>HAND GLOVES ANTI PANAS</t>
+  </si>
+  <si>
+    <t>JAKET COLD STORAGE</t>
+  </si>
+  <si>
+    <t>KANEBO MERAH</t>
+  </si>
+  <si>
+    <t>KERANJANG BUAH / TAHWING</t>
+  </si>
+  <si>
+    <t>KERANJANG DINE IN BAKSO GORENG UK 9X9X5.5</t>
+  </si>
+  <si>
+    <t>KERANJANG PENIRIS</t>
+  </si>
+  <si>
+    <t>KOTAK P3K</t>
+  </si>
+  <si>
+    <t>KUAS OLES BAKSO BAKAR</t>
+  </si>
+  <si>
+    <t>LADLE</t>
+  </si>
+  <si>
+    <t>LAKBAN KARTON BESAR</t>
+  </si>
+  <si>
+    <t>LAKBAN KARTON KECIL</t>
+  </si>
+  <si>
+    <t>MANGKOK STAINLESS PERFORATED BERAS</t>
+  </si>
+  <si>
+    <t>PASTA FORK</t>
+  </si>
+  <si>
+    <t>PEMBUKA KALENG</t>
+  </si>
+  <si>
+    <t>RAK GALON 8 SUSUN KRISBOW RAK GALON BESI 76 X 34 X 132 CM</t>
+  </si>
+  <si>
+    <t>SARINGAN TEPUNG</t>
+  </si>
+  <si>
+    <t>SARUNG TANGAN COLD STORAGE</t>
+  </si>
+  <si>
+    <t>SEPATU BOOT COLD STORAGE</t>
+  </si>
+  <si>
+    <t>SERAGAM LEADER BAKSO</t>
+  </si>
+  <si>
+    <t>SERAGAM LEADER S-XL</t>
+  </si>
+  <si>
+    <t>SERAGAM SAMPLE</t>
+  </si>
+  <si>
+    <t>SPATULA SILICON</t>
+  </si>
+  <si>
+    <t>STEMPEL TANGGAL</t>
+  </si>
+  <si>
+    <t>TERMOGUN INFRARED</t>
+  </si>
+  <si>
+    <t>THERMOMETER RUANG</t>
+  </si>
+  <si>
+    <t>TOPI BAKSO GACOAN</t>
+  </si>
+  <si>
+    <t>TOPI MIE GACOAN</t>
+  </si>
+  <si>
+    <t>WIRE GRILL FOODPAN 1/1 - 100 MM</t>
+  </si>
+  <si>
+    <t>WIRE GRILL FOODPAN 1/2 - 100 MM</t>
+  </si>
+  <si>
+    <t>WIRE GRILL UK. 400X600X30 MM</t>
+  </si>
+  <si>
+    <t>WIRE GRILL UK. 457X660X50 MM</t>
   </si>
 </sst>
 </file>
@@ -1459,7 +1639,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08B8BE52-5B4F-47C1-84A8-24A4E0133727}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B341"/>
+  <dimension ref="A1:B401"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
@@ -4139,7 +4319,7 @@
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A335" s="1" t="s">
+      <c r="A335" t="s">
         <v>340</v>
       </c>
       <c r="B335" t="s">
@@ -4147,7 +4327,7 @@
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A336" s="1" t="s">
+      <c r="A336" t="s">
         <v>340</v>
       </c>
       <c r="B336" t="s">
@@ -4155,7 +4335,7 @@
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A337" s="1" t="s">
+      <c r="A337" t="s">
         <v>340</v>
       </c>
       <c r="B337" t="s">
@@ -4163,7 +4343,7 @@
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A338" s="1" t="s">
+      <c r="A338" t="s">
         <v>340</v>
       </c>
       <c r="B338" t="s">
@@ -4179,7 +4359,7 @@
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A340" s="1" t="s">
+      <c r="A340" t="s">
         <v>65</v>
       </c>
       <c r="B340" t="s">
@@ -4187,14 +4367,495 @@
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A341" s="1" t="s">
+      <c r="A341" t="s">
         <v>340</v>
       </c>
       <c r="B341" t="s">
         <v>354</v>
       </c>
     </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>232</v>
+      </c>
+      <c r="B342" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>10</v>
+      </c>
+      <c r="B343" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>340</v>
+      </c>
+      <c r="B344" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>340</v>
+      </c>
+      <c r="B345" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>38</v>
+      </c>
+      <c r="B346" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>340</v>
+      </c>
+      <c r="B347" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>232</v>
+      </c>
+      <c r="B348" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>340</v>
+      </c>
+      <c r="B349" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>340</v>
+      </c>
+      <c r="B350" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>340</v>
+      </c>
+      <c r="B351" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>65</v>
+      </c>
+      <c r="B352" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>340</v>
+      </c>
+      <c r="B353" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>340</v>
+      </c>
+      <c r="B354" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>340</v>
+      </c>
+      <c r="B355" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>340</v>
+      </c>
+      <c r="B356" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>340</v>
+      </c>
+      <c r="B357" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>340</v>
+      </c>
+      <c r="B358" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>65</v>
+      </c>
+      <c r="B359" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>65</v>
+      </c>
+      <c r="B360" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>65</v>
+      </c>
+      <c r="B361" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>65</v>
+      </c>
+      <c r="B362" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>340</v>
+      </c>
+      <c r="B363" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>340</v>
+      </c>
+      <c r="B364" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>340</v>
+      </c>
+      <c r="B365" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>340</v>
+      </c>
+      <c r="B366" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>340</v>
+      </c>
+      <c r="B367" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>340</v>
+      </c>
+      <c r="B368" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>340</v>
+      </c>
+      <c r="B369" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>340</v>
+      </c>
+      <c r="B370" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>340</v>
+      </c>
+      <c r="B371" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>65</v>
+      </c>
+      <c r="B372" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>38</v>
+      </c>
+      <c r="B373" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>65</v>
+      </c>
+      <c r="B374" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>340</v>
+      </c>
+      <c r="B375" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>340</v>
+      </c>
+      <c r="B376" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>65</v>
+      </c>
+      <c r="B377" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>340</v>
+      </c>
+      <c r="B378" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>340</v>
+      </c>
+      <c r="B379" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>63</v>
+      </c>
+      <c r="B380" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>63</v>
+      </c>
+      <c r="B381" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>340</v>
+      </c>
+      <c r="B382" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>340</v>
+      </c>
+      <c r="B383" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>340</v>
+      </c>
+      <c r="B384" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>65</v>
+      </c>
+      <c r="B385" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>340</v>
+      </c>
+      <c r="B386" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>65</v>
+      </c>
+      <c r="B387" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>65</v>
+      </c>
+      <c r="B388" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>232</v>
+      </c>
+      <c r="B389" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>232</v>
+      </c>
+      <c r="B390" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>232</v>
+      </c>
+      <c r="B391" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>340</v>
+      </c>
+      <c r="B392" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>65</v>
+      </c>
+      <c r="B393" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>65</v>
+      </c>
+      <c r="B394" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>65</v>
+      </c>
+      <c r="B395" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>232</v>
+      </c>
+      <c r="B396" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>232</v>
+      </c>
+      <c r="B397" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>340</v>
+      </c>
+      <c r="B398" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>340</v>
+      </c>
+      <c r="B399" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>340</v>
+      </c>
+      <c r="B400" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>340</v>
+      </c>
+      <c r="B401" t="s">
+        <v>414</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:B401" xr:uid="{08B8BE52-5B4F-47C1-84A8-24A4E0133727}"/>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
